--- a/results/regression_output/full_sample_covid_analysis/extended_control_specifications.xlsx
+++ b/results/regression_output/full_sample_covid_analysis/extended_control_specifications.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,112 +417,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>specification</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>n_controls</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>eu_pre_elasticity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eu_pre_se</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>eu_pre_pval</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>eap_pre_elasticity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>eap_pre_se</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>eap_pre_pval</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>eu_covid_elasticity</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>eu_covid_se</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>eu_covid_pval</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>eap_covid_elasticity</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>eap_covid_se</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>eap_covid_pval</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>price_x_covid_coef</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price_x_covid_pval</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>triple_interaction_coef</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>triple_interaction_pval</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>n_obs</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>r_squared</t>
         </is>
@@ -560,58 +548,58 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2307512919712725</v>
+        <v>-0.1908065607759881</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08011613882156479</v>
+        <v>0.07441262224129772</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004170894996242902</v>
+        <v>0.01067788454604046</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3266158705639082</v>
+        <v>-0.3586832490258667</v>
       </c>
       <c r="I2" t="n">
-        <v>0.156003841127597</v>
+        <v>0.1258002088862993</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03687180626359043</v>
+        <v>0.004563045486056572</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07862122525909832</v>
+        <v>0.1086117580486053</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1352094510115218</v>
+        <v>0.1331184255773259</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5612206948740077</v>
+        <v>0.41500303022429</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08809142046950814</v>
+        <v>0.06278039569190315</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1932180655105882</v>
+        <v>0.1706963681708208</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6486776291532497</v>
+        <v>0.713209218400954</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3093725172303708</v>
+        <v>0.2994183188245934</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0047171955487606</v>
+        <v>0.006939817270934512</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1053347738030455</v>
+        <v>0.1220453258931764</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001870179957691676</v>
+        <v>0.0003131895913697225</v>
       </c>
       <c r="U2" t="n">
         <v>495</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4041421902151686</v>
+        <v>0.4222868362410958</v>
       </c>
     </row>
     <row r="3">
@@ -634,58 +622,58 @@
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1778789626958262</v>
+        <v>-0.1364606944014695</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05233559721715721</v>
+        <v>0.04739380292023907</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000738560271393629</v>
+        <v>0.004180523858242857</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3128960633755908</v>
+        <v>-0.3329291586321067</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1402572362271211</v>
+        <v>0.1114265192535013</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02619399776906817</v>
+        <v>0.00296671404494453</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06940315160896818</v>
+        <v>0.0971936324649034</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08631144288523351</v>
+        <v>0.08260285374182259</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4217736271384878</v>
+        <v>0.2399777433067629</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04365296888240751</v>
+        <v>0.0245511174660307</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1616758604107195</v>
+        <v>0.1370112169452358</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7872848152155436</v>
+        <v>0.8578707430841943</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2472821143047944</v>
+        <v>0.2336543268663729</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003506917450768476</v>
+        <v>0.0006067054574601105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1092669179532039</v>
+        <v>0.1238259492317645</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009437829329074887</v>
+        <v>0.003503187307031919</v>
       </c>
       <c r="U3" t="n">
         <v>495</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3742950513602701</v>
+        <v>0.3824041367382668</v>
       </c>
     </row>
     <row r="4">
@@ -708,58 +696,58 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2007181896571462</v>
+        <v>-0.1432353433987587</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06111605860064765</v>
+        <v>0.05177726682620148</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001104156518723087</v>
+        <v>0.005906518196401533</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3298953016098962</v>
+        <v>-0.3504785606556576</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1442797199706152</v>
+        <v>0.1187486325964152</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02269835986900626</v>
+        <v>0.003331718724750354</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06724403932764389</v>
+        <v>0.09937366898180935</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09929078262762714</v>
+        <v>0.08999448954050022</v>
       </c>
       <c r="M4" t="n">
-        <v>0.49860656678851</v>
+        <v>0.2701000616232445</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0325752091482132</v>
+        <v>0.0108812817654662</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1678677134817271</v>
+        <v>0.1451629858822026</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8462238491533975</v>
+        <v>0.9402812715280882</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2679622289847901</v>
+        <v>0.242609012380568</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0006739709029492946</v>
+        <v>0.001060065235822805</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09450828177331931</v>
+        <v>0.1187508300405558</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007538441403443841</v>
+        <v>0.002731992115759363</v>
       </c>
       <c r="U4" t="n">
         <v>495</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3664480282689816</v>
+        <v>0.379178849657785</v>
       </c>
     </row>
     <row r="5">
@@ -782,58 +770,58 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1609222316540224</v>
+        <v>-0.1593801905328969</v>
       </c>
       <c r="F5" t="n">
-        <v>0.040077131161853</v>
+        <v>0.0393384671571191</v>
       </c>
       <c r="G5" t="n">
-        <v>6.974339522525241e-05</v>
+        <v>6.011233734004584e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3536767928435008</v>
+        <v>-0.3538577295275603</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1391536375299035</v>
+        <v>0.1381615423428651</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01137429962403114</v>
+        <v>0.01076240081793411</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1550562526889133</v>
+        <v>0.155313073613081</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09924888479046998</v>
+        <v>0.0982622259608591</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1189336645852421</v>
+        <v>0.1146853001705139</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04427350880197854</v>
+        <v>0.04370246834340927</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1707591613651468</v>
+        <v>0.1695623367957826</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7955441066996558</v>
+        <v>0.7967299313572329</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3159784843429357</v>
+        <v>0.3146932641459779</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0005511121638330785</v>
+        <v>0.0005221477718919676</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0819718173025437</v>
+        <v>0.08286693372499168</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03795807753536984</v>
+        <v>0.03615780316456352</v>
       </c>
       <c r="U5" t="n">
         <v>495</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3380982422906013</v>
+        <v>0.3384057745921305</v>
       </c>
     </row>
     <row r="6">
@@ -856,58 +844,58 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.158681731329181</v>
+        <v>-0.1569434116500701</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05145175100825338</v>
+        <v>0.05039527186887836</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002170053355405432</v>
+        <v>0.001964314947974444</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3415664048831428</v>
+        <v>-0.3417128272472357</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1551498640578301</v>
+        <v>0.1539856791575077</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0282160471672781</v>
+        <v>0.02698671061535518</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1573035177687853</v>
+        <v>0.1576019215748242</v>
       </c>
       <c r="L6" t="n">
-        <v>0.103941509890437</v>
+        <v>0.1026977164102668</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1308982147924229</v>
+        <v>0.1255943976835276</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05500494209334292</v>
+        <v>0.05443345894513896</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1826023764570556</v>
+        <v>0.1811982683528159</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7633826454143984</v>
+        <v>0.7640073163452419</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3159852490979662</v>
+        <v>0.3145453332248944</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0005149282713838854</v>
+        <v>0.0004849649108555898</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08058609787851953</v>
+        <v>0.08160095296748032</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01624096613805581</v>
+        <v>0.01488536988520317</v>
       </c>
       <c r="U6" t="n">
         <v>495</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3377850176261024</v>
+        <v>0.3381409205256601</v>
       </c>
     </row>
     <row r="7">
@@ -930,58 +918,58 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2175788649683579</v>
+        <v>-0.1553543154909819</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0786557787878671</v>
+        <v>0.06303021255458133</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005909900075440788</v>
+        <v>0.01409154624590658</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3819327537076589</v>
+        <v>-0.4183164000911773</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1519407082073732</v>
+        <v>0.1187380505751605</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01230342646580196</v>
+        <v>0.0004712910068762621</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1402998069794595</v>
+        <v>0.1762019955230177</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1445023363833731</v>
+        <v>0.1321795283334539</v>
       </c>
       <c r="M7" t="n">
-        <v>0.332122920556936</v>
+        <v>0.1832050097293021</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04848656608958578</v>
+        <v>0.01785109638434906</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1961447334036046</v>
+        <v>0.1692039517198653</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8048703717354584</v>
+        <v>0.9160267753934808</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3578786719478174</v>
+        <v>0.3315563110139996</v>
       </c>
       <c r="R7" t="n">
-        <v>0.003322766454101123</v>
+        <v>0.004524901393742731</v>
       </c>
       <c r="S7" t="n">
-        <v>0.07254064784942731</v>
+        <v>0.1046111854615267</v>
       </c>
       <c r="T7" t="n">
-        <v>0.006086718945727876</v>
+        <v>0.001219748587644842</v>
       </c>
       <c r="U7" t="n">
         <v>495</v>
       </c>
       <c r="V7" t="n">
-        <v>0.35443899116738</v>
+        <v>0.3768682934293673</v>
       </c>
     </row>
     <row r="8">
@@ -1004,58 +992,58 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1858391861270978</v>
+        <v>-0.1852893604476891</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05156981770914006</v>
+        <v>0.05092202277400479</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003495518248060048</v>
+        <v>0.000306467766669094</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.348799118411156</v>
+        <v>-0.3506577463163462</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1439827808363816</v>
+        <v>0.142932098770189</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01581586422467063</v>
+        <v>0.01454059203119495</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1455786038060637</v>
+        <v>0.1442811853744973</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1110939482070448</v>
+        <v>0.1094396141579807</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1907392939442316</v>
+        <v>0.1880663167692185</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05396963746291444</v>
+        <v>0.05126825892725741</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1776839339099296</v>
+        <v>0.1760570296726802</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7614695793332582</v>
+        <v>0.7710333112954051</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3314177899331615</v>
+        <v>0.3295705458221864</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0008233132299599877</v>
+        <v>0.0007295185794191639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07135096594090889</v>
+        <v>0.0723554594214172</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03659488849532555</v>
+        <v>0.03593466542724699</v>
       </c>
       <c r="U8" t="n">
         <v>495</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3434810995239769</v>
+        <v>0.3449049784719663</v>
       </c>
     </row>
     <row r="9">
@@ -1078,58 +1066,58 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1691523696373219</v>
+        <v>-0.1676242653923001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04679308956512318</v>
+        <v>0.0459573950991576</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003349653354229876</v>
+        <v>0.0002964299160332917</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3496245898519463</v>
+        <v>-0.3498175481283099</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1481990570104949</v>
+        <v>0.1471080883824976</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01874971572460504</v>
+        <v>0.01783189491473158</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1538514679127076</v>
+        <v>0.1540962292337341</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1059702462373275</v>
+        <v>0.1049409266491931</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1472549035315285</v>
+        <v>0.142702765369304</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04863186698086261</v>
+        <v>0.04806953732053527</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1790738836366883</v>
+        <v>0.1777773313817092</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7860758621862087</v>
+        <v>0.7869847517457584</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3230038375500295</v>
+        <v>0.3217204946260342</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0007422431891261905</v>
+        <v>0.0007087869372151001</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07525261928277946</v>
+        <v>0.07616659082281098</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02153837448492868</v>
+        <v>0.01995679607922374</v>
       </c>
       <c r="U9" t="n">
         <v>495</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3362008196271574</v>
+        <v>0.3365123578311333</v>
       </c>
     </row>
   </sheetData>

--- a/results/regression_output/full_sample_covid_analysis/extended_control_specifications.xlsx
+++ b/results/regression_output/full_sample_covid_analysis/extended_control_specifications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,11 @@
           <t>r_squared</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>df_resid</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -560,28 +565,28 @@
         <v>-0.3586832490258667</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1258002088862993</v>
+        <v>0.1114079656052606</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004563045486056572</v>
+        <v>0.001380347208086219</v>
       </c>
       <c r="K2" t="n">
         <v>0.1086117580486053</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1331184255773259</v>
+        <v>0.07195758655837421</v>
       </c>
       <c r="M2" t="n">
-        <v>0.41500303022429</v>
+        <v>0.1319278750416322</v>
       </c>
       <c r="N2" t="n">
         <v>0.06278039569190315</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1706963681708208</v>
+        <v>0.1179408932434768</v>
       </c>
       <c r="P2" t="n">
-        <v>0.713209218400954</v>
+        <v>0.5947879412813544</v>
       </c>
       <c r="Q2" t="n">
         <v>0.2994183188245934</v>
@@ -600,6 +605,9 @@
       </c>
       <c r="V2" t="n">
         <v>0.4222868362410958</v>
+      </c>
+      <c r="W2" t="n">
+        <v>434</v>
       </c>
     </row>
     <row r="3">
@@ -634,28 +642,28 @@
         <v>-0.3329291586321067</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1114265192535013</v>
+        <v>0.1167778909793696</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00296671404494453</v>
+        <v>0.004564214508270714</v>
       </c>
       <c r="K3" t="n">
         <v>0.0971936324649034</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08260285374182259</v>
+        <v>0.05573016781682696</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2399777433067629</v>
+        <v>0.08185834096701994</v>
       </c>
       <c r="N3" t="n">
         <v>0.0245511174660307</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1370112169452358</v>
+        <v>0.1214375057206401</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8578707430841943</v>
+        <v>0.839876855855858</v>
       </c>
       <c r="Q3" t="n">
         <v>0.2336543268663729</v>
@@ -674,6 +682,9 @@
       </c>
       <c r="V3" t="n">
         <v>0.3824041367382668</v>
+      </c>
+      <c r="W3" t="n">
+        <v>439</v>
       </c>
     </row>
     <row r="4">
@@ -708,28 +719,28 @@
         <v>-0.3504785606556576</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1187486325964152</v>
+        <v>0.1298652008380899</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003331718724750354</v>
+        <v>0.007226513156255443</v>
       </c>
       <c r="K4" t="n">
         <v>0.09937366898180935</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08999448954050022</v>
+        <v>0.05284827609630227</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2701000616232445</v>
+        <v>0.06071815597690922</v>
       </c>
       <c r="N4" t="n">
         <v>0.0108812817654662</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1451629858822026</v>
+        <v>0.1299954669441022</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9402812715280882</v>
+        <v>0.9333288953422176</v>
       </c>
       <c r="Q4" t="n">
         <v>0.242609012380568</v>
@@ -748,6 +759,9 @@
       </c>
       <c r="V4" t="n">
         <v>0.379178849657785</v>
+      </c>
+      <c r="W4" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="5">
@@ -782,28 +796,28 @@
         <v>-0.3538577295275603</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1381615423428651</v>
+        <v>0.1361065710659744</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01076240081793411</v>
+        <v>0.009638456911854165</v>
       </c>
       <c r="K5" t="n">
         <v>0.155313073613081</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0982622259608591</v>
+        <v>0.07820403868661886</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1146853001705139</v>
+        <v>0.04765082758897754</v>
       </c>
       <c r="N5" t="n">
         <v>0.04370246834340927</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1695623367957826</v>
+        <v>0.1353140122663301</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7967299313572329</v>
+        <v>0.7468701235207895</v>
       </c>
       <c r="Q5" t="n">
         <v>0.3146932641459779</v>
@@ -822,6 +836,9 @@
       </c>
       <c r="V5" t="n">
         <v>0.3384057745921305</v>
+      </c>
+      <c r="W5" t="n">
+        <v>442</v>
       </c>
     </row>
     <row r="6">
@@ -856,28 +873,28 @@
         <v>-0.3417128272472357</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1539856791575077</v>
+        <v>0.1309100979924854</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02698671061535518</v>
+        <v>0.009354603047433407</v>
       </c>
       <c r="K6" t="n">
         <v>0.1576019215748242</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1026977164102668</v>
+        <v>0.08081523800364121</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1255943976835276</v>
+        <v>0.05179133588135487</v>
       </c>
       <c r="N6" t="n">
         <v>0.05443345894513896</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1811982683528159</v>
+        <v>0.1321989119521975</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7640073163452419</v>
+        <v>0.6807196342300188</v>
       </c>
       <c r="Q6" t="n">
         <v>0.3145453332248944</v>
@@ -896,6 +913,9 @@
       </c>
       <c r="V6" t="n">
         <v>0.3381409205256601</v>
+      </c>
+      <c r="W6" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="7">
@@ -930,28 +950,28 @@
         <v>-0.4183164000911773</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1187380505751605</v>
+        <v>0.1210348275559162</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0004712910068762621</v>
+        <v>0.0006011351914416707</v>
       </c>
       <c r="K7" t="n">
         <v>0.1762019955230177</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1321795283334539</v>
+        <v>0.07348566307227336</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1832050097293021</v>
+        <v>0.01691086741580072</v>
       </c>
       <c r="N7" t="n">
         <v>0.01785109638434906</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1692039517198653</v>
+        <v>0.1216546957945579</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9160267753934808</v>
+        <v>0.8834077847480817</v>
       </c>
       <c r="Q7" t="n">
         <v>0.3315563110139996</v>
@@ -970,6 +990,9 @@
       </c>
       <c r="V7" t="n">
         <v>0.3768682934293673</v>
+      </c>
+      <c r="W7" t="n">
+        <v>440</v>
       </c>
     </row>
     <row r="8">
@@ -1004,28 +1027,28 @@
         <v>-0.3506577463163462</v>
       </c>
       <c r="I8" t="n">
-        <v>0.142932098770189</v>
+        <v>0.1342793207607255</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01454059203119495</v>
+        <v>0.009324514578489707</v>
       </c>
       <c r="K8" t="n">
         <v>0.1442811853744973</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1094396141579807</v>
+        <v>0.07370603774560643</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1880663167692185</v>
+        <v>0.0509164389700778</v>
       </c>
       <c r="N8" t="n">
         <v>0.05126825892725741</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1760570296726802</v>
+        <v>0.1278369863875255</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7710333112954051</v>
+        <v>0.6885819546299945</v>
       </c>
       <c r="Q8" t="n">
         <v>0.3295705458221864</v>
@@ -1044,6 +1067,9 @@
       </c>
       <c r="V8" t="n">
         <v>0.3449049784719663</v>
+      </c>
+      <c r="W8" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -1078,28 +1104,28 @@
         <v>-0.3498175481283099</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1471080883824976</v>
+        <v>0.1373276326968269</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01783189491473158</v>
+        <v>0.01119232494960265</v>
       </c>
       <c r="K9" t="n">
         <v>0.1540962292337341</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1049409266491931</v>
+        <v>0.07629162331292183</v>
       </c>
       <c r="M9" t="n">
-        <v>0.142702765369304</v>
+        <v>0.04400236755850839</v>
       </c>
       <c r="N9" t="n">
         <v>0.04806953732053527</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1777773313817092</v>
+        <v>0.1373934621959423</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7869847517457584</v>
+        <v>0.7266042441438947</v>
       </c>
       <c r="Q9" t="n">
         <v>0.3217204946260342</v>
@@ -1118,6 +1144,9 @@
       </c>
       <c r="V9" t="n">
         <v>0.3365123578311333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>443</v>
       </c>
     </row>
   </sheetData>
